--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,210.00</t>
+          <t>$2,208.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$1,900.00</t>
+          <t>Price not available</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,648.00</t>
+          <t>$1,647.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Selectorized Seated Leg Curl/Extension</t>
+          <t>Unknown Product</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$5,250.00</t>
+          <t>Price not available</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,208.00</t>
+          <t>$2,204.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,647.00</t>
+          <t>$1,643.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,204.00</t>
+          <t>$2,201.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,643.00</t>
+          <t>$1,642.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,201.00</t>
+          <t>$2,191.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,642.00</t>
+          <t>$1,634.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$845.00</t>
+          <t>Price not available</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Price not available</t>
+          <t>$845.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,191.00</t>
+          <t>$3,063.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,634.00</t>
+          <t>$2,284.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$3,063.90</t>
+          <t>$2,192.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,284.80</t>
+          <t>$1,635.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,192.00</t>
+          <t>$2,190.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,635.00</t>
+          <t>$1,633.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,190.00</t>
+          <t>$2,186.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,633.00</t>
+          <t>$1,630.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,186.00</t>
+          <t>$2,177.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,630.00</t>
+          <t>$1,624.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,177.00</t>
+          <t>$2,172.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,624.00</t>
+          <t>$1,620.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,172.00</t>
+          <t>$2,169.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,620.00</t>
+          <t>$1,617.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,169.00</t>
+          <t>$2,168.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,168.00</t>
+          <t>$2,165.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,617.00</t>
+          <t>$1,614.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,165.00</t>
+          <t>$2,162.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,614.00</t>
+          <t>$1,612.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,162.00</t>
+          <t>$2,153.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,612.00</t>
+          <t>$1,606.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,153.00</t>
+          <t>$2,154.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,154.00</t>
+          <t>$2,151.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,606.00</t>
+          <t>$1,605.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,151.00</t>
+          <t>$2,152.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,152.00</t>
+          <t>$2,149.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,605.00</t>
+          <t>$1,603.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,149.00</t>
+          <t>$2,155.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,603.00</t>
+          <t>$1,607.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,155.00</t>
+          <t>$2,151.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,607.00</t>
+          <t>$1,604.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,151.00</t>
+          <t>$2,150.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,604.00</t>
+          <t>$1,603.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,150.00</t>
+          <t>$2,153.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,603.00</t>
+          <t>$1,606.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,153.00</t>
+          <t>$2,157.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,606.00</t>
+          <t>$1,609.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,157.00</t>
+          <t>$2,159.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,609.00</t>
+          <t>$1,610.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,159.00</t>
+          <t>$2,166.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,610.00</t>
+          <t>$1,615.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,166.00</t>
+          <t>$2,168.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,615.00</t>
+          <t>$1,617.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,168.00</t>
+          <t>$2,178.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,617.00</t>
+          <t>$1,625.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,178.00</t>
+          <t>$2,182.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,625.00</t>
+          <t>$1,627.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,182.00</t>
+          <t>$2,184.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,627.00</t>
+          <t>$1,629.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,184.00</t>
+          <t>$2,185.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,629.00</t>
+          <t>$1,630.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,185.00</t>
+          <t>$2,189.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,630.00</t>
+          <t>$1,633.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,189.00</t>
+          <t>$2,190.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,190.00</t>
+          <t>$2,188.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,633.00</t>
+          <t>$1,632.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,188.00</t>
+          <t>$2,301.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,632.00</t>
+          <t>$1,667.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,301.00</t>
+          <t>$2,311.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,667.00</t>
+          <t>$1,674.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,311.00</t>
+          <t>$2,313.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,674.00</t>
+          <t>$1,675.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/gym_data.xlsx
+++ b/gym_data.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2,313.00</t>
+          <t>$2,311.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$1,675.00</t>
+          <t>$1,674.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
